--- a/artfynd/A 50253-2025 artfynd.xlsx
+++ b/artfynd/A 50253-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2676,6 +2676,134 @@
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>98756273</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hornbäcken (SV Långhällsm.), Området Toften - Långhällsmossen, Upl 608 m NE, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>624235</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6680463</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Östervåla</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2022-02-25</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2022-02-25</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Några få halvtrumningar med långa intervaller. I övrigt tyst.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Kalle Brinell</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Kalle Brinell</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50253-2025 artfynd.xlsx
+++ b/artfynd/A 50253-2025 artfynd.xlsx
@@ -2681,7 +2681,7 @@
         <v>98756273</v>
       </c>
       <c r="B18" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 50253-2025 artfynd.xlsx
+++ b/artfynd/A 50253-2025 artfynd.xlsx
@@ -2681,7 +2681,7 @@
         <v>98756273</v>
       </c>
       <c r="B18" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 50253-2025 artfynd.xlsx
+++ b/artfynd/A 50253-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91733960</v>
+        <v>103870815</v>
       </c>
       <c r="B2" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,49 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långhällsmossen V, Upl</t>
+          <t>syd Långhällsmossen NR, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>624287.3980012339</v>
+        <v>624204</v>
       </c>
       <c r="R2" t="n">
-        <v>6680635.07157458</v>
+        <v>6680624</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-03-20</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>07:28</t>
+          <t>2022-09-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-03-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>07:28</t>
+          <t>2022-09-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,35 +757,35 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>fuktig låga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Gabriel Tjernberg</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Gabriel Tjernberg</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>98518560</v>
+        <v>103870818</v>
       </c>
       <c r="B3" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,49 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hornbäcken (SV Långhällsm.), Området Toften - Långhällsmossen, Upl 608 m NE, Upl</t>
+          <t>syd Långhällsmossen NR, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>624234.4886825903</v>
+        <v>624286</v>
       </c>
       <c r="R3" t="n">
-        <v>6680463.813862841</v>
+        <v>6680541</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,22 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-02-07</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>08:00</t>
+          <t>2022-09-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-02-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2022-09-07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,48 +863,53 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>låga</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kalle Brinell</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kalle Brinell</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>98518605</v>
+        <v>98518560</v>
       </c>
       <c r="B4" t="n">
-        <v>57007</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103042</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -970,7 +926,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -980,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>624234.4886825903</v>
+        <v>624235</v>
       </c>
       <c r="R4" t="n">
-        <v>6680463.813862841</v>
+        <v>6680463</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1052,15 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>98518576</v>
+        <v>98756273</v>
       </c>
       <c r="B5" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1068,46 +1019,50 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hornbäcken (SV Långhällsm.), Området Toften - Långhällsmossen, Upl 728 m NE, Upl</t>
+          <t>Hornbäcken (SV Långhällsm.), Området Toften - Långhällsmossen, Upl 608 m NE, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>624317.4464518018</v>
+        <v>624235</v>
       </c>
       <c r="R5" t="n">
-        <v>6680556.584494196</v>
+        <v>6680463</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1134,22 +1089,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-02-07</t>
+          <t>2022-02-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-02-07</t>
+          <t>2022-02-25</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Några få halvtrumningar med långa intervaller. I övrigt tyst.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1176,42 +1136,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>98953659</v>
+        <v>130711671</v>
       </c>
       <c r="B6" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57811</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100137</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Slaguggla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Strix uralensis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Pallas, 1771</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1221,20 +1176,24 @@
           <t>spel/sång</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hornbäcken (SV Långhällsm.), Området Toften - Långhällsmossen, Upl 608 m NE, Upl</t>
+          <t>Långhällsmossens NR, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>624234.4886825903</v>
+        <v>624086</v>
       </c>
       <c r="R6" t="n">
-        <v>6680463.813862841</v>
+        <v>6680441</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1258,22 +1217,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-03-07</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>09:50</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-03-07</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>09:50</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>&gt;50 inspelade hoanden</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1288,62 +1242,62 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kalle Brinell</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kalle Brinell</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103870815</v>
+        <v>103870821</v>
       </c>
       <c r="B7" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4775</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>100299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>syd Långhällsmossen NR, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>624203.6446155315</v>
+        <v>624136</v>
       </c>
       <c r="R7" t="n">
-        <v>6680624.271128302</v>
+        <v>6680514</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1373,21 +1327,11 @@
           <t>2022-09-07</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-09-07</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1404,7 +1348,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>fuktig låga</t>
+          <t>torrgran</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1422,15 +1366,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103870820</v>
+        <v>103870814</v>
       </c>
       <c r="B8" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>624241.5076789969</v>
+        <v>624248</v>
       </c>
       <c r="R8" t="n">
-        <v>6680476.97341952</v>
+        <v>6680548</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1500,19 +1439,9 @@
           <t>2022-09-07</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-09-07</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1549,15 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>103870821</v>
+        <v>103870820</v>
       </c>
       <c r="B9" t="n">
-        <v>4711</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1565,21 +1489,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100299</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1594,10 +1518,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>624135.7285990764</v>
+        <v>624242</v>
       </c>
       <c r="R9" t="n">
-        <v>6680513.629196898</v>
+        <v>6680477</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1627,19 +1551,9 @@
           <t>2022-09-07</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-09-07</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1676,43 +1590,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>103870819</v>
+        <v>103870822</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1721,10 +1630,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>624252.1590173277</v>
+        <v>624136</v>
       </c>
       <c r="R10" t="n">
-        <v>6680485.783971461</v>
+        <v>6680514</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1754,26 +1663,11 @@
           <t>2022-09-07</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-09-07</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>enstaka</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1786,6 +1680,11 @@
       <c r="AI10" t="inlineStr">
         <is>
           <t>äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>torrgran</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1803,15 +1702,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>103870814</v>
+        <v>103870816</v>
       </c>
       <c r="B11" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>44177</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1819,21 +1713,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>101735</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1848,10 +1742,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>624247.5620389108</v>
+        <v>624352</v>
       </c>
       <c r="R11" t="n">
-        <v>6680547.745924637</v>
+        <v>6680550</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1881,21 +1775,11 @@
           <t>2022-09-07</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-09-07</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1912,7 +1796,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>torrgran</t>
+          <t>björklåga</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1930,53 +1814,64 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>103870818</v>
+        <v>98588429</v>
       </c>
       <c r="B12" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>syd Långhällsmossen NR, Upl</t>
+          <t>Hornbäcken (SV Långhällsm.), Området Toften - Långhällsmossen, Upl 462 m NE, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>624285.6358159847</v>
+        <v>624053</v>
       </c>
       <c r="R12" t="n">
-        <v>6680540.593452007</v>
+        <v>6680459</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2000,22 +1895,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
+          <t>2022-02-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
+          <t>2022-02-12</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2026,41 +1921,26 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>äldre barrskog</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>låga</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Kalle Brinell</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Kalle Brinell</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>103870822</v>
+        <v>98953635</v>
       </c>
       <c r="B13" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2068,42 +1948,49 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100526</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>syd Långhällsmossen NR, Upl</t>
+          <t>Hornbäcken (SV Långhällsm.), Området Toften - Långhällsmossen, Upl 764 m SW, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>624135.7285990764</v>
+        <v>624128</v>
       </c>
       <c r="R13" t="n">
-        <v>6680513.629196898</v>
+        <v>6680483</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2127,22 +2014,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
+          <t>2022-03-07</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
+          <t>2022-03-07</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2153,69 +2040,53 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>äldre barrskog</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>torrgran</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Kalle Brinell</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Kalle Brinell</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>103870817</v>
+        <v>103870813</v>
       </c>
       <c r="B14" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2224,10 +2095,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>624324.3395336417</v>
+        <v>624248</v>
       </c>
       <c r="R14" t="n">
-        <v>6680558.806921928</v>
+        <v>6680548</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2257,26 +2128,11 @@
           <t>2022-09-07</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-09-07</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>1 kvm</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2288,7 +2144,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>äldre barrskog</t>
+          <t>barrskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2306,19 +2162,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>103870813</v>
+        <v>130711662</v>
       </c>
       <c r="B15" t="n">
-        <v>55608</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2344,19 +2195,31 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>syd Långhällsmossen NR, Upl</t>
+          <t>Långhällsmossens NR, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>624247.5620389108</v>
+        <v>624086</v>
       </c>
       <c r="R15" t="n">
-        <v>6680547.745924637</v>
+        <v>6680441</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2380,22 +2243,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>&gt;1200 st inspelade sångstrofer</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2406,36 +2264,26 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>103870816</v>
+        <v>91733885</v>
       </c>
       <c r="B16" t="n">
-        <v>43464</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2443,42 +2291,45 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>101735</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>syd Långhällsmossen NR, Upl</t>
+          <t>Långhällsmossen V, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>624351.5089668215</v>
+        <v>624265</v>
       </c>
       <c r="R16" t="n">
-        <v>6680550.290058829</v>
+        <v>6680623</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2502,22 +2353,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
+          <t>2021-03-20</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>07:17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
+          <t>2021-03-20</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>07:17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2529,57 +2380,47 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>äldre barrskog</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>björklåga</t>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Gabriel Tjernberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Gabriel Tjernberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>98953635</v>
+        <v>98518588</v>
       </c>
       <c r="B17" t="n">
-        <v>55608</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102612</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2589,27 +2430,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hornbäcken (SV Långhällsm.), Området Toften - Långhällsmossen, Upl 764 m SW, Upl</t>
+          <t>Hornbäcken (SV Långhällsm.), Området Toften - Långhällsmossen, Upl 608 m NE, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>624128.2885373052</v>
+        <v>624235</v>
       </c>
       <c r="R17" t="n">
-        <v>6680483.559424894</v>
+        <v>6680463</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2636,22 +2477,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-03-07</t>
+          <t>2022-02-07</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-03-07</t>
+          <t>2022-02-07</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2678,27 +2519,27 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>98756273</v>
+        <v>98518590</v>
       </c>
       <c r="B18" t="n">
-        <v>57741</v>
+        <v>58327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2712,27 +2553,23 @@
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hornbäcken (SV Långhällsm.), Området Toften - Långhällsmossen, Upl 608 m NE, Upl</t>
+          <t>Hornbäcken (SV Långhällsm.), Området Toften - Långhällsmossen, Upl 735 m NE, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>624235</v>
+        <v>624326</v>
       </c>
       <c r="R18" t="n">
-        <v>6680463</v>
+        <v>6680557</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2759,27 +2596,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-02-25</t>
+          <t>2022-02-07</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-02-25</t>
+          <t>2022-02-07</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:56</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Några få halvtrumningar med långa intervaller. I övrigt tyst.</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2803,6 +2635,1539 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>98756315</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hornbäcken (SV Långhällsm.), Området Toften - Långhällsmossen, Upl 645 m NE, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>624238</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6680523</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Östervåla</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2022-02-25</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2022-02-25</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Kalle Brinell</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Kalle Brinell</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>98953702</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Hornbäcken (SV Långhällsm.), Området Toften - Långhällsmossen, Upl 764 m SW, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>624128</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6680483</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Östervåla</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2022-03-07</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2022-03-07</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Kalle Brinell</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Kalle Brinell</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>91733960</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Långhällsmossen V, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>624287</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6680635</v>
+      </c>
+      <c r="S21" t="n">
+        <v>50</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Östervåla</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2021-03-20</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>07:28</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2021-03-20</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>07:28</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Gabriel Tjernberg</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Gabriel Tjernberg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>98518576</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Hornbäcken (SV Långhällsm.), Området Toften - Långhällsmossen, Upl 728 m NE, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>624317</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6680557</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Östervåla</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2022-02-07</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2022-02-07</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Kalle Brinell</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Kalle Brinell</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>98953659</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Hornbäcken (SV Långhällsm.), Området Toften - Långhällsmossen, Upl 608 m NE, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>624235</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6680463</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Östervåla</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2022-03-07</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2022-03-07</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Kalle Brinell</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Kalle Brinell</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>130712332</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Långhällsmossens NR, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>624086</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6680441</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Östervåla</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-04-19</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>&gt;1500 inspelade sång och lock</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>98518605</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58602</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Hornbäcken (SV Långhällsm.), Området Toften - Långhällsmossen, Upl 608 m NE, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>624235</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6680463</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Östervåla</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2022-02-07</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2022-02-07</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Kalle Brinell</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Kalle Brinell</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>98518640</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Hornbäcken (SV Långhällsm.), Området Toften - Långhällsmossen, Upl 608 m NE, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>624235</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6680463</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Östervåla</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2022-02-07</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2022-02-07</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Kalle Brinell</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Kalle Brinell</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>98588478</v>
+      </c>
+      <c r="B27" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Hornbäcken (SV Långhällsm.), Området Toften - Långhällsmossen, Upl 462 m NE, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>624053</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6680459</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Östervåla</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2022-02-12</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2022-02-12</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Kalle Brinell</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Kalle Brinell</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>98953750</v>
+      </c>
+      <c r="B28" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Hornbäcken (SV Långhällsm.), Området Toften - Långhällsmossen, Upl 764 m SW, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>624128</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6680483</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Östervåla</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2022-03-07</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2022-03-07</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Kalle Brinell</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Kalle Brinell</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>98756354</v>
+      </c>
+      <c r="B29" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Hornbäcken (SV Långhällsm.), Området Toften - Långhällsmossen, Upl 462 m NE, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>624053</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6680459</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Östervåla</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2022-02-25</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2022-02-25</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Kalle Brinell</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Kalle Brinell</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>103870817</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>syd Långhällsmossen NR, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>624324</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6680559</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Östervåla</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2022-09-07</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2022-09-07</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>1 kvm</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>103870819</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>syd Långhällsmossen NR, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>624252</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6680486</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Östervåla</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2022-09-07</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2022-09-07</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>enstaka</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50253-2025 artfynd.xlsx
+++ b/artfynd/A 50253-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103870815</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103870818</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98518560</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1133,6 +1153,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98756273</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1251,6 +1276,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130711671</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1363,6 +1393,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103870821</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1475,6 +1510,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103870814</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1587,6 +1627,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103870820</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1699,6 +1744,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103870822</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1811,6 +1861,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103870816</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1934,6 +1989,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98588429</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2053,6 +2113,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98953635</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2159,6 +2224,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103870813</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2277,6 +2347,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130711662</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2397,6 +2472,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91733885</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2516,6 +2596,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98518588</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2635,6 +2720,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98518590</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2754,6 +2844,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98756315</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2873,6 +2968,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98953702</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2997,6 +3097,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91733960</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3116,6 +3221,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98518576</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3235,6 +3345,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98953659</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3349,6 +3464,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130712332</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3468,6 +3588,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98518605</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3587,6 +3712,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98518640</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3706,6 +3836,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98588478</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3825,6 +3960,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98953750</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3944,6 +4084,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98756354</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4056,6 +4201,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103870817</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4168,8 +4318,45 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103870819</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>